--- a/artfynd/A 4223-2026 artfynd.xlsx
+++ b/artfynd/A 4223-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130968741</v>
+        <v>136663287</v>
       </c>
       <c r="B2" t="n">
-        <v>91420</v>
+        <v>93392</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>256335</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485752</v>
+        <v>485691</v>
       </c>
       <c r="R2" t="n">
-        <v>6991168</v>
+        <v>6991178</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-09-01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>kalkbarrskog</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,18 +775,1770 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663287</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136663249</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>485866</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6991178</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663249</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136663305</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Backvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>485783</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6991164</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663305</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136663326</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93436</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Backvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>485782</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6991148</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663326</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136663310</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79474</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Backvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>485819</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6991114</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663310</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136663293</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99366</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Backvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>485843</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6991184</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>i kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663293</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136663277</v>
+      </c>
+      <c r="B8" t="n">
+        <v>110059</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>485632</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6991154</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663277</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136663281</v>
+      </c>
+      <c r="B9" t="n">
+        <v>102468</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Backvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>485874</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6991069</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663281</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136663300</v>
+      </c>
+      <c r="B10" t="n">
+        <v>102468</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Backvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>485857</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6991165</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>i kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663300</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136663291</v>
+      </c>
+      <c r="B11" t="n">
+        <v>103917</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Backvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>485809</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6991194</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>i kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663291</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136663319</v>
+      </c>
+      <c r="B12" t="n">
+        <v>103917</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Backvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>485864</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6991146</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>i kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663319</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136663266</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101454</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>485783</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6991144</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>i kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663266</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136663267</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101454</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>485734</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6991172</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>i kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663267</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136663301</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101454</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Backvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>485851</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6991133</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663301</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136663311</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101454</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Backvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>485706</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6991158</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>i kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663311</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130968741</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91420</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>256335</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ramaria karstenii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Backvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>485752</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6991168</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2017-09-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2017-09-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
           <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ17" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130968741</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136663303</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91599</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>256335</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ramaria karstenii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Backvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>485847</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6991125</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136663303</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4223-2026 artfynd.xlsx
+++ b/artfynd/A 4223-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663287</v>
       </c>
       <c r="B2" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136663249</v>
       </c>
       <c r="B3" t="n">
-        <v>91622</v>
+        <v>91624</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136663305</v>
       </c>
       <c r="B4" t="n">
-        <v>91622</v>
+        <v>91624</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663326</v>
       </c>
       <c r="B5" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663293</v>
       </c>
       <c r="B7" t="n">
-        <v>99366</v>
+        <v>99369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>136663277</v>
       </c>
       <c r="B8" t="n">
-        <v>110059</v>
+        <v>110062</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136663281</v>
       </c>
       <c r="B9" t="n">
-        <v>102468</v>
+        <v>102471</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136663300</v>
       </c>
       <c r="B10" t="n">
-        <v>102468</v>
+        <v>102471</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136663291</v>
       </c>
       <c r="B11" t="n">
-        <v>103917</v>
+        <v>103920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>136663319</v>
       </c>
       <c r="B12" t="n">
-        <v>103917</v>
+        <v>103920</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>136663266</v>
       </c>
       <c r="B13" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>136663267</v>
       </c>
       <c r="B14" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>136663301</v>
       </c>
       <c r="B15" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>136663311</v>
       </c>
       <c r="B16" t="n">
-        <v>101454</v>
+        <v>101457</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136663303</v>
       </c>
       <c r="B18" t="n">
-        <v>91599</v>
+        <v>91601</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4223-2026 artfynd.xlsx
+++ b/artfynd/A 4223-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663287</v>
       </c>
       <c r="B2" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663326</v>
       </c>
       <c r="B5" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663293</v>
       </c>
       <c r="B7" t="n">
-        <v>99369</v>
+        <v>99370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>136663277</v>
       </c>
       <c r="B8" t="n">
-        <v>110062</v>
+        <v>110063</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136663281</v>
       </c>
       <c r="B9" t="n">
-        <v>102471</v>
+        <v>102472</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136663300</v>
       </c>
       <c r="B10" t="n">
-        <v>102471</v>
+        <v>102472</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136663291</v>
       </c>
       <c r="B11" t="n">
-        <v>103920</v>
+        <v>103921</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>136663319</v>
       </c>
       <c r="B12" t="n">
-        <v>103920</v>
+        <v>103921</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>136663266</v>
       </c>
       <c r="B13" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>136663267</v>
       </c>
       <c r="B14" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>136663301</v>
       </c>
       <c r="B15" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>136663311</v>
       </c>
       <c r="B16" t="n">
-        <v>101457</v>
+        <v>101458</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 4223-2026 artfynd.xlsx
+++ b/artfynd/A 4223-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663287</v>
       </c>
       <c r="B2" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136663249</v>
       </c>
       <c r="B3" t="n">
-        <v>91624</v>
+        <v>91626</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136663305</v>
       </c>
       <c r="B4" t="n">
-        <v>91624</v>
+        <v>91626</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663326</v>
       </c>
       <c r="B5" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136663310</v>
       </c>
       <c r="B6" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663293</v>
       </c>
       <c r="B7" t="n">
-        <v>99370</v>
+        <v>99375</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>136663277</v>
       </c>
       <c r="B8" t="n">
-        <v>110063</v>
+        <v>110068</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136663281</v>
       </c>
       <c r="B9" t="n">
-        <v>102472</v>
+        <v>102477</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136663300</v>
       </c>
       <c r="B10" t="n">
-        <v>102472</v>
+        <v>102477</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136663291</v>
       </c>
       <c r="B11" t="n">
-        <v>103921</v>
+        <v>103926</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>136663319</v>
       </c>
       <c r="B12" t="n">
-        <v>103921</v>
+        <v>103926</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>136663266</v>
       </c>
       <c r="B13" t="n">
-        <v>101458</v>
+        <v>101463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>136663267</v>
       </c>
       <c r="B14" t="n">
-        <v>101458</v>
+        <v>101463</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>136663301</v>
       </c>
       <c r="B15" t="n">
-        <v>101458</v>
+        <v>101463</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>136663311</v>
       </c>
       <c r="B16" t="n">
-        <v>101458</v>
+        <v>101463</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136663303</v>
       </c>
       <c r="B18" t="n">
-        <v>91601</v>
+        <v>91603</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4223-2026 artfynd.xlsx
+++ b/artfynd/A 4223-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663287</v>
       </c>
       <c r="B2" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136663249</v>
       </c>
       <c r="B3" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136663305</v>
       </c>
       <c r="B4" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663326</v>
       </c>
       <c r="B5" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663293</v>
       </c>
       <c r="B7" t="n">
-        <v>99375</v>
+        <v>99377</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>136663277</v>
       </c>
       <c r="B8" t="n">
-        <v>110068</v>
+        <v>110070</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136663281</v>
       </c>
       <c r="B9" t="n">
-        <v>102477</v>
+        <v>102479</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136663300</v>
       </c>
       <c r="B10" t="n">
-        <v>102477</v>
+        <v>102479</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136663291</v>
       </c>
       <c r="B11" t="n">
-        <v>103926</v>
+        <v>103928</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>136663319</v>
       </c>
       <c r="B12" t="n">
-        <v>103926</v>
+        <v>103928</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>136663266</v>
       </c>
       <c r="B13" t="n">
-        <v>101463</v>
+        <v>101465</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>136663267</v>
       </c>
       <c r="B14" t="n">
-        <v>101463</v>
+        <v>101465</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>136663301</v>
       </c>
       <c r="B15" t="n">
-        <v>101463</v>
+        <v>101465</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>136663311</v>
       </c>
       <c r="B16" t="n">
-        <v>101463</v>
+        <v>101465</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136663303</v>
       </c>
       <c r="B18" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4223-2026 artfynd.xlsx
+++ b/artfynd/A 4223-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663287</v>
       </c>
       <c r="B2" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136663249</v>
       </c>
       <c r="B3" t="n">
-        <v>91628</v>
+        <v>91630</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136663305</v>
       </c>
       <c r="B4" t="n">
-        <v>91628</v>
+        <v>91630</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663326</v>
       </c>
       <c r="B5" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136663310</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663293</v>
       </c>
       <c r="B7" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>136663277</v>
       </c>
       <c r="B8" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136663281</v>
       </c>
       <c r="B9" t="n">
-        <v>102479</v>
+        <v>102485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136663300</v>
       </c>
       <c r="B10" t="n">
-        <v>102479</v>
+        <v>102485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136663291</v>
       </c>
       <c r="B11" t="n">
-        <v>103928</v>
+        <v>103934</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>136663319</v>
       </c>
       <c r="B12" t="n">
-        <v>103928</v>
+        <v>103934</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>136663266</v>
       </c>
       <c r="B13" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>136663267</v>
       </c>
       <c r="B14" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>136663301</v>
       </c>
       <c r="B15" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>136663311</v>
       </c>
       <c r="B16" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136663303</v>
       </c>
       <c r="B18" t="n">
-        <v>91605</v>
+        <v>91607</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4223-2026 artfynd.xlsx
+++ b/artfynd/A 4223-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663287</v>
       </c>
       <c r="B2" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136663249</v>
       </c>
       <c r="B3" t="n">
-        <v>91630</v>
+        <v>91632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136663305</v>
       </c>
       <c r="B4" t="n">
-        <v>91630</v>
+        <v>91632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663326</v>
       </c>
       <c r="B5" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136663310</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663293</v>
       </c>
       <c r="B7" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>136663277</v>
       </c>
       <c r="B8" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136663281</v>
       </c>
       <c r="B9" t="n">
-        <v>102485</v>
+        <v>102487</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136663300</v>
       </c>
       <c r="B10" t="n">
-        <v>102485</v>
+        <v>102487</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136663291</v>
       </c>
       <c r="B11" t="n">
-        <v>103934</v>
+        <v>103936</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>136663319</v>
       </c>
       <c r="B12" t="n">
-        <v>103934</v>
+        <v>103936</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>136663266</v>
       </c>
       <c r="B13" t="n">
-        <v>101471</v>
+        <v>101473</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>136663267</v>
       </c>
       <c r="B14" t="n">
-        <v>101471</v>
+        <v>101473</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>136663301</v>
       </c>
       <c r="B15" t="n">
-        <v>101471</v>
+        <v>101473</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>136663311</v>
       </c>
       <c r="B16" t="n">
-        <v>101471</v>
+        <v>101473</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136663303</v>
       </c>
       <c r="B18" t="n">
-        <v>91607</v>
+        <v>91609</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4223-2026 artfynd.xlsx
+++ b/artfynd/A 4223-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663287</v>
       </c>
       <c r="B2" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136663249</v>
       </c>
       <c r="B3" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136663305</v>
       </c>
       <c r="B4" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663326</v>
       </c>
       <c r="B5" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136663310</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663293</v>
       </c>
       <c r="B7" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>136663277</v>
       </c>
       <c r="B8" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136663281</v>
       </c>
       <c r="B9" t="n">
-        <v>102487</v>
+        <v>102488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136663300</v>
       </c>
       <c r="B10" t="n">
-        <v>102487</v>
+        <v>102488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136663291</v>
       </c>
       <c r="B11" t="n">
-        <v>103936</v>
+        <v>103937</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>136663319</v>
       </c>
       <c r="B12" t="n">
-        <v>103936</v>
+        <v>103937</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>136663266</v>
       </c>
       <c r="B13" t="n">
-        <v>101473</v>
+        <v>101474</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>136663267</v>
       </c>
       <c r="B14" t="n">
-        <v>101473</v>
+        <v>101474</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>136663301</v>
       </c>
       <c r="B15" t="n">
-        <v>101473</v>
+        <v>101474</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>136663311</v>
       </c>
       <c r="B16" t="n">
-        <v>101473</v>
+        <v>101474</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136663303</v>
       </c>
       <c r="B18" t="n">
-        <v>91609</v>
+        <v>91610</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4223-2026 artfynd.xlsx
+++ b/artfynd/A 4223-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663287</v>
       </c>
       <c r="B2" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136663249</v>
       </c>
       <c r="B3" t="n">
-        <v>91633</v>
+        <v>91639</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136663305</v>
       </c>
       <c r="B4" t="n">
-        <v>91633</v>
+        <v>91639</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663326</v>
       </c>
       <c r="B5" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663293</v>
       </c>
       <c r="B7" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>136663277</v>
       </c>
       <c r="B8" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136663281</v>
       </c>
       <c r="B9" t="n">
-        <v>102488</v>
+        <v>102494</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136663300</v>
       </c>
       <c r="B10" t="n">
-        <v>102488</v>
+        <v>102494</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136663291</v>
       </c>
       <c r="B11" t="n">
-        <v>103937</v>
+        <v>103943</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>136663319</v>
       </c>
       <c r="B12" t="n">
-        <v>103937</v>
+        <v>103943</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>136663266</v>
       </c>
       <c r="B13" t="n">
-        <v>101474</v>
+        <v>101480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>136663267</v>
       </c>
       <c r="B14" t="n">
-        <v>101474</v>
+        <v>101480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>136663301</v>
       </c>
       <c r="B15" t="n">
-        <v>101474</v>
+        <v>101480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>136663311</v>
       </c>
       <c r="B16" t="n">
-        <v>101474</v>
+        <v>101480</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136663303</v>
       </c>
       <c r="B18" t="n">
-        <v>91610</v>
+        <v>91616</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4223-2026 artfynd.xlsx
+++ b/artfynd/A 4223-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663287</v>
       </c>
       <c r="B2" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136663249</v>
       </c>
       <c r="B3" t="n">
-        <v>91639</v>
+        <v>91643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136663305</v>
       </c>
       <c r="B4" t="n">
-        <v>91639</v>
+        <v>91643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663326</v>
       </c>
       <c r="B5" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136663310</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663293</v>
       </c>
       <c r="B7" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>136663277</v>
       </c>
       <c r="B8" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136663281</v>
       </c>
       <c r="B9" t="n">
-        <v>102494</v>
+        <v>102498</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136663300</v>
       </c>
       <c r="B10" t="n">
-        <v>102494</v>
+        <v>102498</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136663291</v>
       </c>
       <c r="B11" t="n">
-        <v>103943</v>
+        <v>103947</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>136663319</v>
       </c>
       <c r="B12" t="n">
-        <v>103943</v>
+        <v>103947</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>136663266</v>
       </c>
       <c r="B13" t="n">
-        <v>101480</v>
+        <v>101484</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>136663267</v>
       </c>
       <c r="B14" t="n">
-        <v>101480</v>
+        <v>101484</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>136663301</v>
       </c>
       <c r="B15" t="n">
-        <v>101480</v>
+        <v>101484</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>136663311</v>
       </c>
       <c r="B16" t="n">
-        <v>101480</v>
+        <v>101484</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136663303</v>
       </c>
       <c r="B18" t="n">
-        <v>91616</v>
+        <v>91620</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4223-2026 artfynd.xlsx
+++ b/artfynd/A 4223-2026 artfynd.xlsx
@@ -1213,7 +1213,7 @@
         <v>136663293</v>
       </c>
       <c r="B7" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>136663277</v>
       </c>
       <c r="B8" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136663281</v>
       </c>
       <c r="B9" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136663300</v>
       </c>
       <c r="B10" t="n">
-        <v>102498</v>
+        <v>102500</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136663291</v>
       </c>
       <c r="B11" t="n">
-        <v>103947</v>
+        <v>103949</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>136663319</v>
       </c>
       <c r="B12" t="n">
-        <v>103947</v>
+        <v>103949</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>136663266</v>
       </c>
       <c r="B13" t="n">
-        <v>101484</v>
+        <v>101486</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>136663267</v>
       </c>
       <c r="B14" t="n">
-        <v>101484</v>
+        <v>101486</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>136663301</v>
       </c>
       <c r="B15" t="n">
-        <v>101484</v>
+        <v>101486</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>136663311</v>
       </c>
       <c r="B16" t="n">
-        <v>101484</v>
+        <v>101486</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 4223-2026 artfynd.xlsx
+++ b/artfynd/A 4223-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663287</v>
       </c>
       <c r="B2" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136663249</v>
       </c>
       <c r="B3" t="n">
-        <v>91643</v>
+        <v>91645</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136663305</v>
       </c>
       <c r="B4" t="n">
-        <v>91643</v>
+        <v>91645</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663326</v>
       </c>
       <c r="B5" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136663310</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663293</v>
       </c>
       <c r="B7" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>136663277</v>
       </c>
       <c r="B8" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136663281</v>
       </c>
       <c r="B9" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136663300</v>
       </c>
       <c r="B10" t="n">
-        <v>102500</v>
+        <v>102502</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136663291</v>
       </c>
       <c r="B11" t="n">
-        <v>103949</v>
+        <v>103951</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>136663319</v>
       </c>
       <c r="B12" t="n">
-        <v>103949</v>
+        <v>103951</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>136663266</v>
       </c>
       <c r="B13" t="n">
-        <v>101486</v>
+        <v>101488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>136663267</v>
       </c>
       <c r="B14" t="n">
-        <v>101486</v>
+        <v>101488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>136663301</v>
       </c>
       <c r="B15" t="n">
-        <v>101486</v>
+        <v>101488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>136663311</v>
       </c>
       <c r="B16" t="n">
-        <v>101486</v>
+        <v>101488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136663303</v>
       </c>
       <c r="B18" t="n">
-        <v>91620</v>
+        <v>91622</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4223-2026 artfynd.xlsx
+++ b/artfynd/A 4223-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663287</v>
       </c>
       <c r="B2" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136663249</v>
       </c>
       <c r="B3" t="n">
-        <v>91645</v>
+        <v>91658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136663305</v>
       </c>
       <c r="B4" t="n">
-        <v>91645</v>
+        <v>91658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663326</v>
       </c>
       <c r="B5" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136663310</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663293</v>
       </c>
       <c r="B7" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>136663277</v>
       </c>
       <c r="B8" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136663281</v>
       </c>
       <c r="B9" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136663300</v>
       </c>
       <c r="B10" t="n">
-        <v>102502</v>
+        <v>102515</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136663291</v>
       </c>
       <c r="B11" t="n">
-        <v>103951</v>
+        <v>103964</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>136663319</v>
       </c>
       <c r="B12" t="n">
-        <v>103951</v>
+        <v>103964</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>136663266</v>
       </c>
       <c r="B13" t="n">
-        <v>101488</v>
+        <v>101501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>136663267</v>
       </c>
       <c r="B14" t="n">
-        <v>101488</v>
+        <v>101501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>136663301</v>
       </c>
       <c r="B15" t="n">
-        <v>101488</v>
+        <v>101501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>136663311</v>
       </c>
       <c r="B16" t="n">
-        <v>101488</v>
+        <v>101501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136663303</v>
       </c>
       <c r="B18" t="n">
-        <v>91622</v>
+        <v>91635</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4223-2026 artfynd.xlsx
+++ b/artfynd/A 4223-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663287</v>
       </c>
       <c r="B2" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136663249</v>
       </c>
       <c r="B3" t="n">
-        <v>91658</v>
+        <v>91660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136663305</v>
       </c>
       <c r="B4" t="n">
-        <v>91658</v>
+        <v>91660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663326</v>
       </c>
       <c r="B5" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136663310</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663293</v>
       </c>
       <c r="B7" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>136663277</v>
       </c>
       <c r="B8" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136663281</v>
       </c>
       <c r="B9" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136663300</v>
       </c>
       <c r="B10" t="n">
-        <v>102515</v>
+        <v>102517</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136663291</v>
       </c>
       <c r="B11" t="n">
-        <v>103964</v>
+        <v>103966</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>136663319</v>
       </c>
       <c r="B12" t="n">
-        <v>103964</v>
+        <v>103966</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>136663266</v>
       </c>
       <c r="B13" t="n">
-        <v>101501</v>
+        <v>101503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>136663267</v>
       </c>
       <c r="B14" t="n">
-        <v>101501</v>
+        <v>101503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>136663301</v>
       </c>
       <c r="B15" t="n">
-        <v>101501</v>
+        <v>101503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>136663311</v>
       </c>
       <c r="B16" t="n">
-        <v>101501</v>
+        <v>101503</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136663303</v>
       </c>
       <c r="B18" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4223-2026 artfynd.xlsx
+++ b/artfynd/A 4223-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136663287</v>
       </c>
       <c r="B2" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136663249</v>
       </c>
       <c r="B3" t="n">
-        <v>91660</v>
+        <v>91663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136663305</v>
       </c>
       <c r="B4" t="n">
-        <v>91660</v>
+        <v>91663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136663326</v>
       </c>
       <c r="B5" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>136663293</v>
       </c>
       <c r="B7" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>136663277</v>
       </c>
       <c r="B8" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>136663281</v>
       </c>
       <c r="B9" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         <v>136663300</v>
       </c>
       <c r="B10" t="n">
-        <v>102517</v>
+        <v>102520</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>136663291</v>
       </c>
       <c r="B11" t="n">
-        <v>103966</v>
+        <v>103969</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>136663319</v>
       </c>
       <c r="B12" t="n">
-        <v>103966</v>
+        <v>103969</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>136663266</v>
       </c>
       <c r="B13" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>136663267</v>
       </c>
       <c r="B14" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>136663301</v>
       </c>
       <c r="B15" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>136663311</v>
       </c>
       <c r="B16" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>136663303</v>
       </c>
       <c r="B18" t="n">
-        <v>91637</v>
+        <v>91640</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
